--- a/teacher_forms/012_teaching_assistant_questionnaire--teacher_forms.xlsx
+++ b/teacher_forms/012_teaching_assistant_questionnaire--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Phone call'}</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
